--- a/tests/fixtures/baseline/multi-3src__yidao/000.xlsx
+++ b/tests/fixtures/baseline/multi-3src__yidao/000.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F29"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -910,9 +910,89 @@
         <v>64001.47</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>张三</v>
+      </c>
+      <c r="B26" t="str">
+        <v>42082119860805901X</v>
+      </c>
+      <c r="C26" t="str">
+        <v>13800138498</v>
+      </c>
+      <c r="D26" t="str">
+        <v>建设银行</v>
+      </c>
+      <c r="E26" t="str">
+        <v>6217000000000000247</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5200.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>李四</v>
+      </c>
+      <c r="B27" t="str">
+        <v>42082119860805901X</v>
+      </c>
+      <c r="C27" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="D27" t="str">
+        <v>中国银行</v>
+      </c>
+      <c r="E27" t="str">
+        <v>6216616200012345678</v>
+      </c>
+      <c r="F27" t="str">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>王五</v>
+      </c>
+      <c r="B28" t="str">
+        <v>11010119900307421X</v>
+      </c>
+      <c r="C28" t="str">
+        <v>13900139000</v>
+      </c>
+      <c r="D28" t="str">
+        <v>工商银行</v>
+      </c>
+      <c r="E28" t="str">
+        <v>6,266.80</v>
+      </c>
+      <c r="F28" t="str">
+        <v>4266.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>赵六</v>
+      </c>
+      <c r="B29" t="str">
+        <v>11010119900307421X</v>
+      </c>
+      <c r="C29" t="str">
+        <v>13700137000</v>
+      </c>
+      <c r="D29" t="str">
+        <v>农业银行</v>
+      </c>
+      <c r="E29" t="str">
+        <v>6228480000000007342</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F29"/>
   </ignoredErrors>
 </worksheet>
 </file>